--- a/assets/xlsx/cards-pages/cards.gov.xlsx
+++ b/assets/xlsx/cards-pages/cards.gov.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF60"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,6 +577,11 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>is_ad</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -586,12 +591,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -636,12 +641,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>直辖市</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -686,12 +691,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>直辖市</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -736,12 +741,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>直辖市</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -786,12 +791,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>直辖市</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -836,12 +841,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -886,12 +891,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -936,12 +941,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -986,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1036,12 +1041,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1086,12 +1091,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1136,12 +1141,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1186,12 +1191,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1236,12 +1241,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1286,12 +1291,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1336,12 +1341,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1386,12 +1391,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1436,12 +1441,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1486,12 +1491,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1536,12 +1541,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1586,12 +1591,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1636,12 +1641,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1686,12 +1691,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1736,12 +1741,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1786,12 +1791,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1836,12 +1841,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1886,12 +1891,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>省</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1936,12 +1941,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>自治区</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1986,12 +1991,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>自治区</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2036,12 +2041,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>自治区</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2086,12 +2091,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>自治区</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2136,12 +2141,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>自治区</t>
+          <t>人大</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2186,7 +2191,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2236,7 +2241,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2286,7 +2291,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2336,7 +2341,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2386,7 +2391,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2436,7 +2441,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2486,7 +2491,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2536,7 +2541,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2586,7 +2591,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2636,7 +2641,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2686,7 +2691,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2736,7 +2741,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2786,7 +2791,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2836,7 +2841,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2886,7 +2891,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2936,7 +2941,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2986,7 +2991,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3036,7 +3041,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3086,7 +3091,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3136,7 +3141,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3186,7 +3191,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3236,7 +3241,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3286,7 +3291,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3336,7 +3341,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3386,7 +3391,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3436,7 +3441,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3486,7 +3491,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>directory/gov</t>
+          <t>topics/gov</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
